--- a/VerveStacks_ESP/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ESP/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ESP\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{62C9CF43-1E87-4978-A617-8C81E0876552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B758A8E7-C242-4973-B91F-9E13B2587A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ESP/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ESP/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ESP\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B758A8E7-C242-4973-B91F-9E13B2587A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{817C81A8-6A33-4D5D-AF52-EB23A6989AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ESP/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ESP/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ESP\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{817C81A8-6A33-4D5D-AF52-EB23A6989AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{29D4BD85-B749-4EA1-95A1-9C7F342BADC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
